--- a/data/trans_orig/P36BPD03_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD03_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de raciones de verdura u hortalizas que consume al día en 2023</t>
+          <t>Población según el número de raciones de verdura u hortalizas que consume al día en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20977</t>
+          <t>21054</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>65134</t>
+          <t>63296</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,47 +745,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>5,26%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>15,82%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>28707</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>16415</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>49734</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>5,24%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,28%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>28707</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>17049</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>47298</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>9,17%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>5,44%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43886</t>
+          <t>45028</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95732</t>
+          <t>97524</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90026</t>
+          <t>88694</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>154628</t>
+          <t>155958</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67005</t>
+          <t>64844</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>109893</t>
+          <t>106806</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>165061</t>
+          <t>168343</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>247234</t>
+          <t>244464</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,28%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>133386</t>
+          <t>134499</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>202963</t>
+          <t>202100</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>125042</t>
+          <t>126064</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>172682</t>
+          <t>172403</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>273224</t>
+          <t>273868</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>356790</t>
+          <t>358690</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>50,29%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48613</t>
+          <t>51642</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>107230</t>
+          <t>109473</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32758</t>
+          <t>32480</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64874</t>
+          <t>65919</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>93746</t>
+          <t>93672</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>162582</t>
+          <t>164558</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>23,07%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12214</t>
+          <t>12121</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36117</t>
+          <t>36710</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11965</t>
+          <t>12206</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33983</t>
+          <t>35152</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>28873</t>
+          <t>29621</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>62021</t>
+          <t>61921</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>107109</t>
+          <t>105928</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>154625</t>
+          <t>155692</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64806</t>
+          <t>66503</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>129135</t>
+          <t>129861</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>181684</t>
+          <t>177032</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>273751</t>
+          <t>271814</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,1%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>150668</t>
+          <t>153649</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>202497</t>
+          <t>205500</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>249811</t>
+          <t>250854</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>378224</t>
+          <t>371696</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>413984</t>
+          <t>418347</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>581213</t>
+          <t>589426</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>63,1%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>74126</t>
+          <t>74549</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>119843</t>
+          <t>117194</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>56912</t>
+          <t>59113</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>116623</t>
+          <t>117502</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>142588</t>
+          <t>142237</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>222081</t>
+          <t>225619</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,15%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21791</t>
+          <t>22956</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>46291</t>
+          <t>46387</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15323</t>
+          <t>16233</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31960</t>
+          <t>32365</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>42606</t>
+          <t>43084</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>71131</t>
+          <t>72052</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>110171</t>
+          <t>108875</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>152530</t>
+          <t>150438</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>93101</t>
+          <t>93550</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>124785</t>
+          <t>125414</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>212839</t>
+          <t>214774</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>265962</t>
+          <t>265736</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,64%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>223844</t>
+          <t>225606</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>272096</t>
+          <t>274661</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>267166</t>
+          <t>266771</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>304906</t>
+          <t>306222</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>503177</t>
+          <t>502897</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>565947</t>
+          <t>563994</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,29%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>104876</t>
+          <t>104409</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>145813</t>
+          <t>147943</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>109047</t>
+          <t>108870</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>141632</t>
+          <t>140778</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>222658</t>
+          <t>225654</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>276748</t>
+          <t>279199</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,88%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13367</t>
+          <t>14316</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55575</t>
+          <t>55581</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18636</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34121</t>
+          <t>34164</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>37596</t>
+          <t>38346</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>79301</t>
+          <t>81316</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>68506</t>
+          <t>72423</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>228320</t>
+          <t>230232</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>103808</t>
+          <t>104795</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>145355</t>
+          <t>145701</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>165222</t>
+          <t>175660</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>345445</t>
+          <t>349988</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>406363</t>
+          <t>404375</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>738684</t>
+          <t>746784</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>355928</t>
+          <t>357341</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>434962</t>
+          <t>449963</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>795367</t>
+          <t>790715</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1216591</t>
+          <t>1173648</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>73,37%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>66767</t>
+          <t>59771</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>214345</t>
+          <t>215662</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>148369</t>
+          <t>148167</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>197268</t>
+          <t>196989</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>204742</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>394927</t>
+          <t>396411</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,78%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>27426</t>
+          <t>27908</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>49768</t>
+          <t>52522</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13513</t>
+          <t>13548</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27225</t>
+          <t>26650</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>45186</t>
+          <t>46396</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>71064</t>
+          <t>73347</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>100268</t>
+          <t>98642</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>136098</t>
+          <t>136225</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>83078</t>
+          <t>84092</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>111057</t>
+          <t>110177</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>192222</t>
+          <t>192880</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>237466</t>
+          <t>237573</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>270375</t>
+          <t>271331</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>316727</t>
+          <t>315448</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>275332</t>
+          <t>277601</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>310946</t>
+          <t>313749</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>559924</t>
+          <t>560408</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>613245</t>
+          <t>614937</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,53%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>93880</t>
+          <t>93624</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>128234</t>
+          <t>129022</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>123266</t>
+          <t>122218</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>152704</t>
+          <t>153918</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>225387</t>
+          <t>226047</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>269875</t>
+          <t>274247</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11587</t>
+          <t>11022</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26098</t>
+          <t>25342</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>22898</t>
+          <t>23074</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>15548</t>
+          <t>14303</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>43632</t>
+          <t>43260</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>61396</t>
+          <t>62470</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>87208</t>
+          <t>87050</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>25197</t>
+          <t>24481</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>98138</t>
+          <t>98436</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>72903</t>
+          <t>69648</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>178250</t>
+          <t>179293</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>176433</t>
+          <t>176373</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>207061</t>
+          <t>208143</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>89746</t>
+          <t>89514</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>345497</t>
+          <t>345109</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>227552</t>
+          <t>197847</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>533511</t>
+          <t>533884</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>54,78%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>70839</t>
+          <t>70571</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>97115</t>
+          <t>96268</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>149460</t>
+          <t>150584</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>484071</t>
+          <t>490577</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>230730</t>
+          <t>229769</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>657556</t>
+          <t>684517</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>70,23%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6137</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>16557</t>
+          <t>17232</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>12568</t>
+          <t>12276</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>24609</t>
+          <t>24434</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>21683</t>
+          <t>20800</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>37137</t>
+          <t>37030</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>49114</t>
+          <t>48693</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>70639</t>
+          <t>70195</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>71687</t>
+          <t>71966</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>94705</t>
+          <t>94236</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>126136</t>
+          <t>126820</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>157314</t>
+          <t>157938</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>142776</t>
+          <t>143865</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>169491</t>
+          <t>169593</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>231782</t>
+          <t>230353</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>259277</t>
+          <t>258645</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>381387</t>
+          <t>382486</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>419715</t>
+          <t>422911</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,85%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>45544</t>
+          <t>46587</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>68105</t>
+          <t>67464</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>68203</t>
+          <t>68345</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>91456</t>
+          <t>90833</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>120638</t>
+          <t>120222</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>151877</t>
+          <t>152380</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,57%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>146993</t>
+          <t>147908</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>232120</t>
+          <t>231074</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>122314</t>
+          <t>119156</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>178828</t>
+          <t>176357</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>292912</t>
+          <t>289812</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>391298</t>
+          <t>396371</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>615160</t>
+          <t>611618</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>873605</t>
+          <t>873185</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>552938</t>
+          <t>539289</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>729524</t>
+          <t>727584</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1270836</t>
+          <t>1259283</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1572321</t>
+          <t>1560238</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1634802</t>
+          <t>1630212</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2159107</t>
+          <t>2174827</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1568687</t>
+          <t>1516610</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2025855</t>
+          <t>2013123</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>3370696</t>
+          <t>3338519</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>3982010</t>
+          <t>4033644</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,7%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>546491</t>
+          <t>515693</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>771246</t>
+          <t>769711</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>786749</t>
+          <t>792028</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1443537</t>
+          <t>1492821</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1445624</t>
+          <t>1451596</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2160847</t>
+          <t>2320061</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>32,61%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD03_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD03_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>37270</t>
+          <t>32366</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21054</t>
+          <t>17517</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63296</t>
+          <t>54719</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>28707</t>
+          <t>29518</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16415</t>
+          <t>17895</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49734</t>
+          <t>47044</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>65977</t>
+          <t>61884</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45028</t>
+          <t>40951</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>97524</t>
+          <t>88576</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>120240</t>
+          <t>107520</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88694</t>
+          <t>82142</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>155958</t>
+          <t>135658</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>85631</t>
+          <t>94539</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64844</t>
+          <t>73739</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>106806</t>
+          <t>118625</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>205871</t>
+          <t>202059</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>168343</t>
+          <t>167421</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>244464</t>
+          <t>239694</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>31,12%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>166481</t>
+          <t>182377</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>134499</t>
+          <t>148754</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>202100</t>
+          <t>213294</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>150350</t>
+          <t>180401</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>126064</t>
+          <t>155944</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>172403</t>
+          <t>207957</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>316831</t>
+          <t>362779</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>273868</t>
+          <t>320963</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>358690</t>
+          <t>401679</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>52,15%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>75995</t>
+          <t>85530</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51642</t>
+          <t>59925</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>109473</t>
+          <t>118326</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>48512</t>
+          <t>58053</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32480</t>
+          <t>40385</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65919</t>
+          <t>80450</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>124507</t>
+          <t>143583</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>93672</t>
+          <t>112208</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>164558</t>
+          <t>191947</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>24,92%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21720</t>
+          <t>26433</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>15193</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36710</t>
+          <t>41769</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21804</t>
+          <t>22839</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12206</t>
+          <t>14619</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35152</t>
+          <t>34263</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>43524</t>
+          <t>49271</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29621</t>
+          <t>34910</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>66494</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>130319</t>
+          <t>135098</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>105928</t>
+          <t>112827</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155692</t>
+          <t>162482</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>103977</t>
+          <t>114704</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>66503</t>
+          <t>95188</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>129861</t>
+          <t>135325</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>234296</t>
+          <t>249803</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>177032</t>
+          <t>216338</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>271814</t>
+          <t>282214</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,89%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>176664</t>
+          <t>202631</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>153649</t>
+          <t>175118</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>205500</t>
+          <t>231936</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>292112</t>
+          <t>250686</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>250854</t>
+          <t>226300</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>371696</t>
+          <t>274790</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>468776</t>
+          <t>453318</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>418347</t>
+          <t>416070</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>589426</t>
+          <t>492198</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>50,38%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>94844</t>
+          <t>112728</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>74549</t>
+          <t>88537</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>117194</t>
+          <t>140165</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>92739</t>
+          <t>111879</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59113</t>
+          <t>93928</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>117502</t>
+          <t>135609</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>187583</t>
+          <t>224606</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>142237</t>
+          <t>194086</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>225619</t>
+          <t>259064</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>26,52%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>510633</t>
+          <t>500108</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>510633</t>
+          <t>500108</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>510633</t>
+          <t>500108</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>934180</t>
+          <t>976998</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>934180</t>
+          <t>976998</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>934180</t>
+          <t>976998</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>32962</t>
+          <t>35444</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22956</t>
+          <t>24935</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>46387</t>
+          <t>50513</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>22787</t>
+          <t>23639</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16233</t>
+          <t>16146</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32365</t>
+          <t>33184</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>55749</t>
+          <t>59083</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>43084</t>
+          <t>45778</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>72052</t>
+          <t>77854</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>129979</t>
+          <t>140689</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>108875</t>
+          <t>121035</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>150438</t>
+          <t>164349</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>108586</t>
+          <t>118612</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>93550</t>
+          <t>101927</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>125414</t>
+          <t>135016</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>238564</t>
+          <t>259301</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>214774</t>
+          <t>233359</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>265736</t>
+          <t>287566</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>248136</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>225606</t>
+          <t>271620</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>274661</t>
+          <t>324614</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>286503</t>
+          <t>333940</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>266771</t>
+          <t>312625</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>306222</t>
+          <t>356289</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>534638</t>
+          <t>630575</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>502897</t>
+          <t>595949</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>563994</t>
+          <t>663775</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>53,45%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>125098</t>
+          <t>146951</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>104409</t>
+          <t>123429</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>147943</t>
+          <t>171065</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>124593</t>
+          <t>145948</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>108870</t>
+          <t>128060</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>140778</t>
+          <t>165704</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>249690</t>
+          <t>292899</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>225654</t>
+          <t>264672</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>279199</t>
+          <t>323435</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,04%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>536175</t>
+          <t>619719</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>536175</t>
+          <t>619719</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>536175</t>
+          <t>619719</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1078642</t>
+          <t>1241858</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1078642</t>
+          <t>1241858</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1078642</t>
+          <t>1241858</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>34973</t>
+          <t>35606</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14316</t>
+          <t>24986</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55581</t>
+          <t>49307</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25802</t>
+          <t>27850</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18636</t>
+          <t>20838</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34164</t>
+          <t>36809</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>60775</t>
+          <t>63457</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>38346</t>
+          <t>50532</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81316</t>
+          <t>78585</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>157396</t>
+          <t>164986</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>72423</t>
+          <t>142377</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>230232</t>
+          <t>187797</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>126092</t>
+          <t>128422</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>104795</t>
+          <t>112571</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>145701</t>
+          <t>142620</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>283488</t>
+          <t>293408</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>175660</t>
+          <t>266096</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>349988</t>
+          <t>321451</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>547754</t>
+          <t>333651</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>404375</t>
+          <t>306920</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>746784</t>
+          <t>363189</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>383585</t>
+          <t>384784</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>357341</t>
+          <t>363153</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>449963</t>
+          <t>406285</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>931339</t>
+          <t>718435</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>790715</t>
+          <t>682849</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1173648</t>
+          <t>754191</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>52,51%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>147663</t>
+          <t>166373</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59771</t>
+          <t>144631</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>215662</t>
+          <t>190833</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>176332</t>
+          <t>194680</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>148167</t>
+          <t>175784</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>196989</t>
+          <t>215041</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>323994</t>
+          <t>361054</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>204742</t>
+          <t>331481</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>396411</t>
+          <t>391544</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>27,26%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>711810</t>
+          <t>735737</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>711810</t>
+          <t>735737</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>711810</t>
+          <t>735737</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1599596</t>
+          <t>1436354</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1599596</t>
+          <t>1436354</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1599596</t>
+          <t>1436354</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>37681</t>
+          <t>38222</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>27908</t>
+          <t>27936</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>52522</t>
+          <t>50934</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>19570</t>
+          <t>21314</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13548</t>
+          <t>14997</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26650</t>
+          <t>29680</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>57251</t>
+          <t>59536</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>46396</t>
+          <t>47867</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>73347</t>
+          <t>74491</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>117534</t>
+          <t>125795</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>98642</t>
+          <t>108725</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>136225</t>
+          <t>146771</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>95974</t>
+          <t>104923</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>84092</t>
+          <t>92176</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>110177</t>
+          <t>119765</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>213508</t>
+          <t>230717</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>192880</t>
+          <t>208790</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>237573</t>
+          <t>257078</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>293827</t>
+          <t>318322</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>271331</t>
+          <t>294005</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>315448</t>
+          <t>341105</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>294618</t>
+          <t>324195</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>277601</t>
+          <t>304653</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>313749</t>
+          <t>344572</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>588445</t>
+          <t>642517</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>560408</t>
+          <t>612240</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>614937</t>
+          <t>672886</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,32%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>110454</t>
+          <t>125205</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>93624</t>
+          <t>105935</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>129022</t>
+          <t>144977</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>137743</t>
+          <t>158424</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>122218</t>
+          <t>141936</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>153918</t>
+          <t>175939</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>248197</t>
+          <t>283629</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>226047</t>
+          <t>257667</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>274247</t>
+          <t>307824</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>25,31%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>559496</t>
+          <t>607544</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>559496</t>
+          <t>607544</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>559496</t>
+          <t>607544</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1107401</t>
+          <t>1216399</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1107401</t>
+          <t>1216399</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1107401</t>
+          <t>1216399</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>17447</t>
+          <t>19666</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11022</t>
+          <t>12706</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>25342</t>
+          <t>27537</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>13344</t>
+          <t>15125</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>10533</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>23074</t>
+          <t>22266</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>30791</t>
+          <t>34791</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>14303</t>
+          <t>25795</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>43260</t>
+          <t>46476</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>74040</t>
+          <t>79287</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>62470</t>
+          <t>65870</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>87050</t>
+          <t>91820</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>61611</t>
+          <t>66244</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>24481</t>
+          <t>56015</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>98436</t>
+          <t>77231</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>135651</t>
+          <t>145531</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>69648</t>
+          <t>130503</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>179293</t>
+          <t>163982</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>19,43%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>192256</t>
+          <t>209214</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>176373</t>
+          <t>192879</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>208143</t>
+          <t>228082</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>224246</t>
+          <t>240808</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>89514</t>
+          <t>226582</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>345109</t>
+          <t>256492</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>416502</t>
+          <t>450022</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>197847</t>
+          <t>427302</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>533884</t>
+          <t>471948</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>55,91%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>83616</t>
+          <t>97909</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>70571</t>
+          <t>82472</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>96268</t>
+          <t>112800</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>308072</t>
+          <t>115874</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>150584</t>
+          <t>101292</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>490577</t>
+          <t>128601</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>391687</t>
+          <t>213783</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>229769</t>
+          <t>195259</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>684517</t>
+          <t>234763</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>27,81%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>367358</t>
+          <t>406075</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>367358</t>
+          <t>406075</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>367358</t>
+          <t>406075</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>607273</t>
+          <t>438051</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>607273</t>
+          <t>438051</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>607273</t>
+          <t>438051</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>974631</t>
+          <t>844126</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>974631</t>
+          <t>844126</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>974631</t>
+          <t>844126</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>10414</t>
+          <t>11081</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>6377</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>17232</t>
+          <t>17641</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>17649</t>
+          <t>18492</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>12276</t>
+          <t>13074</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>24434</t>
+          <t>25871</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>28063</t>
+          <t>29573</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>20800</t>
+          <t>21618</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>37030</t>
+          <t>37777</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>58620</t>
+          <t>62735</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>48693</t>
+          <t>51577</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>70195</t>
+          <t>73758</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>82581</t>
+          <t>87698</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>71966</t>
+          <t>75304</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>94236</t>
+          <t>99734</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>141201</t>
+          <t>150433</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>126820</t>
+          <t>134317</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>157938</t>
+          <t>167287</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>156759</t>
+          <t>171129</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>143865</t>
+          <t>155369</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>169593</t>
+          <t>184866</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>245076</t>
+          <t>268004</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>230353</t>
+          <t>252785</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>258645</t>
+          <t>283880</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>401835</t>
+          <t>439133</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>382486</t>
+          <t>418040</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>422911</t>
+          <t>462007</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>59,79%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>56225</t>
+          <t>64485</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>46587</t>
+          <t>52987</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>67464</t>
+          <t>78094</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>79281</t>
+          <t>89139</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>68345</t>
+          <t>76881</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>90833</t>
+          <t>102698</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>135506</t>
+          <t>153624</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>120222</t>
+          <t>136818</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>152380</t>
+          <t>172296</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>282018</t>
+          <t>309430</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>282018</t>
+          <t>309430</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>282018</t>
+          <t>309430</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>424588</t>
+          <t>463333</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>424588</t>
+          <t>463333</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>424588</t>
+          <t>463333</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>706605</t>
+          <t>772763</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>706605</t>
+          <t>772763</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>706605</t>
+          <t>772763</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>192468</t>
+          <t>198818</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>147908</t>
+          <t>166558</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>231074</t>
+          <t>229718</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>149662</t>
+          <t>158776</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>119156</t>
+          <t>135677</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>176357</t>
+          <t>183486</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>342130</t>
+          <t>357595</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>289812</t>
+          <t>321645</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>396371</t>
+          <t>401872</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>788127</t>
+          <t>816110</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>611618</t>
+          <t>762333</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>873185</t>
+          <t>876476</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>664452</t>
+          <t>715142</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>539289</t>
+          <t>673310</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>727584</t>
+          <t>761989</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>1452580</t>
+          <t>1531252</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1259283</t>
+          <t>1463105</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1560238</t>
+          <t>1604072</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>1781878</t>
+          <t>1713959</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1630212</t>
+          <t>1649591</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2174827</t>
+          <t>1774853</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>1876489</t>
+          <t>1982819</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1516610</t>
+          <t>1928696</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2013123</t>
+          <t>2036507</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>3658368</t>
+          <t>3696778</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>3338519</t>
+          <t>3609249</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>4033644</t>
+          <t>3787107</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>52,17%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>693893</t>
+          <t>799182</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>515693</t>
+          <t>743701</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>769711</t>
+          <t>859366</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>967272</t>
+          <t>873997</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>792028</t>
+          <t>826194</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1492821</t>
+          <t>915618</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>1661166</t>
+          <t>1673179</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1451596</t>
+          <t>1600795</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2320061</t>
+          <t>1746180</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>3456366</t>
+          <t>3528069</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3456366</t>
+          <t>3528069</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3456366</t>
+          <t>3528069</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>3657876</t>
+          <t>3730735</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3657876</t>
+          <t>3730735</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3657876</t>
+          <t>3730735</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>7114243</t>
+          <t>7258804</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>7114243</t>
+          <t>7258804</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7114243</t>
+          <t>7258804</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
